--- a/data/daily/2026-10/2026-10-31.xlsx
+++ b/data/daily/2026-10/2026-10-31.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="카카오선물하기" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="올리브영" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="올리브영_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1394,261 +1392,6 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2084,21 +1827,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16393</v>
+        <v>16396</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>빠른 활력 및 피로 회복 — 피로할 때 섭취 시 에너지가 올라가고 몸이 한결 가벼워짐</t>
+          <t>뛰어난 피로 회복 효과 — 마신 후 에너지가 올라가고 몸이 한결 가벼워짐</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>편리한 듀얼 포뮬러 — 정제와 액상을 물 없이 한 번에 간편하게 섭취할 수 있음</t>
+          <t>간편한 휴대 및 섭취 — 정제와 액상이 함께 있어 물 없이도 간편하게 섭취함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 기프트박스 포장이 깔끔하여 생일이나 환절기 선물로 적합함</t>
+          <t>고급스러운 포장 디자인 — 기프트박스 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2143,26 +1886,26 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15723</v>
+        <v>15724</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 포장이 깔끔하고 고급스러워 선물받을 때 기분이 좋아짐</t>
+          <t>간편한 올인원 구성 — 액상과 정제가 함께 있어 다양한 영양소를 한 번에 간편하게 챙김</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 액상·알약 구성 — 마시는 액상과 알약이 함께 들어 있어 비타민 섭취가 편리함</t>
+          <t>고급스러운 패키지 — 포장이 깔끔하고 고급스러워 선물용으로 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>부담 없는 10입 단위 — 10개입 한 박스 구성이라 무난하게 선물하고 챙겨 먹기 적당함</t>
+          <t>합리적인 가격대 — 가격이 합리적이고 실용적인 키링 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>쇼핑백 미동봉 아쉬움 — 선물용으로 적합하나 쇼핑백이 따로 동봉되지 않음</t>
+          <t>선물용 쇼핑백 누락 — 선물용 쇼핑백이 따로 동봉되지 않음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2210,22 +1953,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>하루 한 병 간편한 섭취 — 여러 영양제를 챙길 필요 없이 하루 한 병으로 섭취가 완료됨</t>
+          <t>넉넉한 용량 구성 — 30+3입 구성으로 한 달 이상 넉넉하게 복용함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>넉넉한 30+3입 구성 — 한 달 넘게 먹을 수 있는 넉넉한 용량이라 온 가족이 나누어 먹기 좋음</t>
+          <t>확실한 체력 증진 — 에너지 충전 및 면역력 강화에 효과적임</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>체감되는 에너지 충전 — 속이 편안하며 체력 증진 및 에너지 활력 충전에 효과적임</t>
+          <t>간편한 1일 1병 섭취 — 하루 한 병으로 영양을 편하게 관리함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 제품 품질과 효능은 만족스러우나 가격대가 높게 느껴짐</t>
+          <t>부담스러운 가격 — 제품 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2269,21 +2012,21 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6551</v>
+        <v>6552</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>간편한 구미 제형 — 알약과 달리 젤리 형태로 되어 있어 물 없이 간식처럼 섭취함</t>
+          <t>맛있는 젤리 제형 — 달지 않고 과일 향이 살아서 간식처럼 맛있게 먹음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>부담 없는 달콤한 과일 맛 — 지나치게 달지 않고 상큼한 과일 향이 나서 맛있게 챙겨 먹기 좋음</t>
+          <t>편리한 구미 섭취 방식 — 물 없이 씹어 먹는 구미 형태로 복용 부담을 줄임</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>넉넉한 80구미 용량 — 80개입으로 구성되어 넉넉하게 복용 가능함</t>
+          <t>온 가족 복용 가능 — 남녀노소 누구나 함께 복용하기에 적합함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2332,22 +2075,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1포 개별 포장 휴대성 — 컴팩트한 포 형태로 되어 있어 가방에 넣거나 여행 시 들고 다니기 좋음</t>
+          <t>개별 포장 및 휴대성 — 개별 포 형태로 포장되어 가방에 넣고 다니거나 여행 시 들고 가기 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 섭취 후 피로가 줄어들고 에너지가 생기는 듯한 기분이 듦</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>깔끔하고 예쁜 패키지 — 포장이 예쁘고 깔끔하여 주변 지인이나 자신을 위한 선물로 적합함</t>
-        </is>
-      </c>
+          <t>빠른 활력 충전 효과 — 복용 후 기운이 나는 듯한 활력 증진을 느낌</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>배송 중 박스 구김 — 배송 과정에서 제품 박스가 구겨져 도착하는 아쉬움이 있음</t>
+          <t>배송 중 상자 훼손 — 배송 과정에서 제품 박스가 구겨져서 도착함</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2395,19 +2134,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>액상·정제 복합 제형 — 알약과 액상 비타민이 같이 들어 있어 효과가 배가되는 느낌을 줌</t>
+          <t>액상 정제 이중 구성 — 액상과 정제를 함께 먹어 빠른 피로 회복감을 느낌</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>환절기 건강 및 피로 케어 — 꾸준히 먹으면 몸과 마음이 상쾌해지고 일상 버티기에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>만족도 높은 선물 구성 — 받는 사람에게 필요한 선물로 구성과 배송 만족도가 높음</t>
-        </is>
-      </c>
+          <t>상큼한 맛과 빠른 배송 — 상큼한 맛과 빠른 배송 및 알찬 구성에 만족함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2450,21 +2185,21 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8776</v>
+        <v>8778</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>알찬 7+2 증정 구성 — 7입에 2입이 추가 증정되어 실속 있고 넉넉하게 섭취 가능함</t>
+          <t>물 없는 간편한 섭취 — 상단 정제와 오렌지맛 액상을 물 없이 간편하게 복용함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>넉넉한 유통기한 — 개봉을 늦게 하더라도 유통기한이 넉넉하여 안심하고 복용함</t>
+          <t>넉넉한 추가 증정 — 7입에 2입이 더해진 9입 구성으로 여분이 있어 반가움</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>합리적인 가격대 — 좋은 구성의 제품을 착한 가격으로 구매할 수 있음</t>
+          <t>우수한 피로 회복 — 복용 후 피로가 풀어지고 에너지가 생김</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -2513,17 +2248,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>액상·분말 혼합 캡슐 — 버튼을 누르면 액상과 분말이 섞이는 방식으로 누르고 마시기 편함</t>
+          <t>신선한 믹스형 용기 — 버튼을 눌러 액상과 분말을 직접 섞어 마시는 바이탈 캡 형태임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>목걸림 없는 가루 제형 — 알약 섭취 시 목에 걸리는 불편함 없이 편하게 복용할 수 있음</t>
+          <t>목넘김 편한 가루 제형 — 가루 형태로 되어 있어 알약 이물감 없이 편하게 복용함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>맛있고 빠른 피로 회복 — 달달하고 상큼한 맛이며 섭취 후 피로 해소와 체력 충전 효과가 뛰어남</t>
+          <t>우수한 피로 회복 효과 — 달콤상큼한 맛이며 피로 완화 및 혓바늘 개선에 도움을 줌</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -2572,18 +2307,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 바쁘거나 체력이 떨어질 때 복용 시 활력이 돋고 몸이 가벼워짐</t>
+          <t>확실한 활력 개선 — 바쁜 일상이나 피로 상황에서 체력 및 활력 증진을 체감함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리하고 빠른 배송 — 배송 상태가 양호하며 편리하게 챙겨 먹기 좋음</t>
+          <t>안전한 배송 및 복용 — 포장 배송 상태가 양호하며 먹기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>호불호 갈리는 감기약 맛 — 오렌지 맛 감기약 느낌의 향과 맛이 나서 호불호가 존재함</t>
+          <t>약 맛 감기약 느낌 — 오렌지 맛 감기약 느낌이 나 맛에 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2631,22 +2366,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 및 구성 — 유사 제품 대비 합리적인 가격과 알찬 성분 구성을 자랑함</t>
+          <t>뛰어난 실속과 가성비 — 타 브랜드 대비 성분과 가격 면에서 실속 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>체감되는 건강 개선 — 복용 후 기대 이상으로 피로 회복 및 체력 관리 효과를 체감함</t>
+          <t>체감되는 피로 회복 — 복용 후 몸이 느낄 정도로 피로 회복 효과가 뛰어남</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>간편한 일체형 휴대성 — 하루 한 병씩 챙겨 다니며 간편하게 복용할 수 있음</t>
+          <t>부담 없는 맛 — 맛이 괜찮아 매일 거부감 없이 복용 가능함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>쇼핑백 미동봉 배송 — 선물용 구매 시 쇼핑백이 동봉되지 않아 아쉬움이 있음</t>
+          <t>쇼핑백 누락 — 쇼핑백이 동봉되지 않아 아쉬움</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2694,22 +2429,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지가 정성스럽고 고급스러워 선물용으로 만족도가 높음</t>
+          <t>고급스러운 선물 포장 — 오간자 및 플리츠백 구성으로 패키지가 고급스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 맛 — 비린 맛 없이 맛있게 마실 수 있어 꾸준한 복용이 용이함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>피부 탄력 관리 도움 — 하루 한 병 섭취로 피부가 촉촉해지고 탄력이 생기는 기분이 듦</t>
-        </is>
-      </c>
+          <t>거부감 없는 맛 — 콜라겐 특유의 거부감 없이 맛있게 복용함</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>오간자 포장 누락 — 오간자 포장이 누락된 상태로 배송되는 경우가 발생함</t>
+          <t>오간자 포장 누락 — 안내된 오간자 포장이 누락되어 배송됨</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2757,22 +2488,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>풍성한 혜택 및 알찬 구성 — 효소와 단백질바, 포토카드까지 포함된 가성비 높고 알찬 구성임</t>
+          <t>알찬 기획 구성 — 효소와 단백질바, 포토카드까지 포함되어 기획 구성이 알참</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>맛있는 가루 효소 — 크림소다, 베리말차 등 다양한 맛이 있어 거부감 없이 맛있음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>속 편한 소화 개선 — 위가 불편할 때 먹기 좋으며 영양을 간편하게 챙길 수 있음</t>
-        </is>
-      </c>
+          <t>맛있는 효소 풍미 — 크림소다, 베리말차 등 여러 맛이 모두 맛있음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>증정 포토카드 구김 — 배송 포장 상태로 인해 증정 포토카드가 일부 구겨져 도착함</t>
+          <t>포토카드 구겨짐 — 증정 포토카드 일부가 구겨진 상태로 도착함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -2820,17 +2547,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 속이 편안하고 빠른 회복이 가능함</t>
+          <t>확실한 숙취 해소 — 음주 전후 상관없이 복용 시 다음 날 속이 편안함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>개별 포장의 우수한 휴대성 — 1포씩 깔끔하게 개별 포장되어 가방에 넣고 다니기 편리함</t>
+          <t>개별 포장 및 휴대성 — 개별 스틱 포장으로 가방에 하나씩 휴대하기 좋음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>넉넉한 15포 세트 구성 — 5포씩 3박스로 나뉘어 넉넉하게 보관하고 지인에게 나눌 수 있음</t>
+          <t>알찬 3박스 세트 — 15포 세트 구성으로 넉넉하며 선물용으로 포장이 깔끔함</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2879,17 +2606,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 더부룩함이 줄어들고 소화가 잘 되며 장 건강에 도움을 줌</t>
+          <t>속 편한 소화 촉진 — 더부룩한 속을 줄여주고 소화 및 배변 활동을 도움</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소한 맛이라 부담 없이 먹기 좋음</t>
+          <t>고소한 미숫가루 맛 — 텁텁함 없이 미숫가루처럼 구수하고 맛있음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>풍성한 사은품 증정 — 추가 증정포와 견과류바 등 푸짐한 구성 혜택이 제공됨</t>
+          <t>푸짐한 사은품 제공 — 견과류 박스 등 푸짐한 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2938,17 +2665,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 다양한 종류와 맛으로 구성되어 식단 관리 시 질리지 않음</t>
+          <t>다채로운 20종 구성 — 20가지 다채로운 구성으로 질리지 않고 섭취 가능함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 부드러워 부담 없이 맛있게 즐길 수 있음</t>
+          <t>부드러운 닭가슴살 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 부드러움</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>전자레인지용 용기 증정 — 증정된 용기로 전자레인지에 간편하게 데워 먹을 수 있음</t>
+          <t>전용 용기 제공 — 전자레인지용 용기가 함께 제공되어 편리함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2997,19 +2724,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>거부감 없는 달콤한 맛 — 비린 맛없이 달콤한 두유나 음료 느낌으로 맛있게 마실 수 있음</t>
+          <t>비린 맛 없는 음료 감각 — 단백질 특유의 비린 맛이 없고 달달하여 음료처럼 마심</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>포만감 및 간식 대용 — 마시면 배가 차서 간식이 당길 때나 포만감 유지에 도움 됨</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>운동 후 단백질 보충 — 운동 후 간편하게 마시며 단백질을 챙기기에 적합함</t>
-        </is>
-      </c>
+          <t>포만감 및 단백질 충전 — 은근히 포만감이 있고 운동 후 단백질 보충에 유용함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3056,17 +2779,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>식후 빠른 소화 촉진 — 음식 섭취 후 복용 시 속이 편안해지고 소화가 잘 됨</t>
+          <t>우수한 소화 개선 — 식사 후 복용 시 소화를 한결 잘되게 해줌</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>고소한 옥수수 맛 — 거부감 없는 옥수수 맛이며 물 없이도 간편하게 섭취 가능함</t>
+          <t>고소한 옥수수 맛 — 옥수수 맛이라 거부감이 없고 물 없이 복용 가능함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>맛있는 저당 견과류바 증정 — 사은품으로 함께 제공되는 저당 견과류바의 맛과 퀄리티가 우수함</t>
+          <t>맛있는 사은품 증정 — 사은품으로 증정되는 저당 견과류바의 맛과 만족도가 높음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3115,17 +2838,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 복용 시 피로가 줄고 운동 수행 능력 및 에너지가 개선됨</t>
+          <t>운동 수행 능력 향상 — 복용 시 피로가 줄고 운동 수행 능력 향상에 도움을 줌</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>고운 입자와 뛰어난 용해도 — 입자가 아주 고와서 물에 잘 녹아 섭취하기 편함</t>
+          <t>고운 입자와 우수한 용해 — 입자가 매우 고와 물에 잘 녹음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>대용량 및 뛰어난 가성비 — 100서빙의 넉넉한 용량 대비 가격이 저렴하여 가성비가 훌륭함</t>
+          <t>높은 가성비 — 100서빙의 대용량 대비 가격이 저렴함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3143,55 +2866,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"2개월분" 김종국 듀얼 아르기닌 &amp; 밀크씨슬 플러스 + 쇼핑백 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1535</v>
+        <v>75</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>아르기닌·밀크씨슬 올인원 — 활력과 간 건강을 동시에 챙길 수 있는 알찬 2개월분 구성임</t>
+          <t>다양한 맛 구성 — 여러 종류의 맛으로 구성되어 질리지 않게 식단 관리함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 복용 후 아침 일어남이 가벼워지고 일상 피로감이 줄어듦</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>운동 및 일상 활력 증진 — 운동 집중도가 높아지고 컨디션 관리에 큰 도움이 됨</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>쇼핑백 끈 불량 배송 — 증정용 쇼핑백의 끈이 달려있지 않은 불량 상태로 배송됨</t>
-        </is>
-      </c>
+          <t>촉촉한 식감과 빠른 조리 — 닭가슴살이 촉촉하며 전자레인지로 간편하게 조리함</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3206,51 +2921,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>"2개월분" 김종국 듀얼 아르기닌 &amp; 밀크씨슬 플러스 + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>75</v>
+        <v>1535</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다채로운 맛 구성 — 종류가 다양하여 매일 질리지 않고 식단 관리를 할 수 있음</t>
+          <t>활력과 간 건강 케어 — 아르기닌과 밀크씨슬을 한 번에 섭취할 수 있어 효율적임</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 맛이 뛰어남</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>간편한 전자레인지 조리 — 전자레인지에 쉽게 데워 먹을 수 있어 식사 대용으로 편리함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>피로 감소 효과 — 복용 후 피로가 감소하고 아침에 일어날 때 몸이 한결 가벼움</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>쇼핑백 끈 누락 — 증정 쇼핑백에 끈이 달리지 않은 상태로 배송됨</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3572,16 +3287,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16393</v>
+        <v>16396</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15723</v>
+        <v>15724</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3434</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6551</v>
+        <v>6552</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>110</v>
@@ -3590,7 +3305,7 @@
         <v>836</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8776</v>
+        <v>8778</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1828</v>
@@ -3610,71 +3325,69 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>빠른 활력 및 피로 회복 — 피로할 때 섭취 시 에너지가 올라가고 몸이 한결 가벼워짐
-편리한 듀얼 포뮬러 — 정제와 액상을 물 없이 한 번에 간편하게 섭취할 수 있음
-고급스러운 선물용 포장 — 기프트박스 포장이 깔끔하여 생일이나 환절기 선물로 적합함</t>
+          <t>뛰어난 피로 회복 효과 — 마신 후 에너지가 올라가고 몸이 한결 가벼워짐
+간편한 휴대 및 섭취 — 정제와 액상이 함께 있어 물 없이도 간편하게 섭취함
+고급스러운 포장 디자인 — 기프트박스 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 포장이 깔끔하고 고급스러워 선물받을 때 기분이 좋아짐
-간편한 액상·알약 구성 — 마시는 액상과 알약이 함께 들어 있어 비타민 섭취가 편리함
-부담 없는 10입 단위 — 10개입 한 박스 구성이라 무난하게 선물하고 챙겨 먹기 적당함</t>
+          <t>간편한 올인원 구성 — 액상과 정제가 함께 있어 다양한 영양소를 한 번에 간편하게 챙김
+고급스러운 패키지 — 포장이 깔끔하고 고급스러워 선물용으로 좋음
+합리적인 가격대 — 가격이 합리적이고 실용적인 키링 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>하루 한 병 간편한 섭취 — 여러 영양제를 챙길 필요 없이 하루 한 병으로 섭취가 완료됨
-넉넉한 30+3입 구성 — 한 달 넘게 먹을 수 있는 넉넉한 용량이라 온 가족이 나누어 먹기 좋음
-체감되는 에너지 충전 — 속이 편안하며 체력 증진 및 에너지 활력 충전에 효과적임</t>
+          <t>넉넉한 용량 구성 — 30+3입 구성으로 한 달 이상 넉넉하게 복용함
+확실한 체력 증진 — 에너지 충전 및 면역력 강화에 효과적임
+간편한 1일 1병 섭취 — 하루 한 병으로 영양을 편하게 관리함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>간편한 구미 제형 — 알약과 달리 젤리 형태로 되어 있어 물 없이 간식처럼 섭취함
-부담 없는 달콤한 과일 맛 — 지나치게 달지 않고 상큼한 과일 향이 나서 맛있게 챙겨 먹기 좋음
-넉넉한 80구미 용량 — 80개입으로 구성되어 넉넉하게 복용 가능함</t>
+          <t>맛있는 젤리 제형 — 달지 않고 과일 향이 살아서 간식처럼 맛있게 먹음
+편리한 구미 섭취 방식 — 물 없이 씹어 먹는 구미 형태로 복용 부담을 줄임
+온 가족 복용 가능 — 남녀노소 누구나 함께 복용하기에 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1포 개별 포장 휴대성 — 컴팩트한 포 형태로 되어 있어 가방에 넣거나 여행 시 들고 다니기 좋음
-체감되는 활력 증진 — 섭취 후 피로가 줄어들고 에너지가 생기는 듯한 기분이 듦
-깔끔하고 예쁜 패키지 — 포장이 예쁘고 깔끔하여 주변 지인이나 자신을 위한 선물로 적합함</t>
+          <t>개별 포장 및 휴대성 — 개별 포 형태로 포장되어 가방에 넣고 다니거나 여행 시 들고 가기 용이함
+빠른 활력 충전 효과 — 복용 후 기운이 나는 듯한 활력 증진을 느낌</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>액상·정제 복합 제형 — 알약과 액상 비타민이 같이 들어 있어 효과가 배가되는 느낌을 줌
-환절기 건강 및 피로 케어 — 꾸준히 먹으면 몸과 마음이 상쾌해지고 일상 버티기에 도움이 됨
-만족도 높은 선물 구성 — 받는 사람에게 필요한 선물로 구성과 배송 만족도가 높음</t>
+          <t>액상 정제 이중 구성 — 액상과 정제를 함께 먹어 빠른 피로 회복감을 느낌
+상큼한 맛과 빠른 배송 — 상큼한 맛과 빠른 배송 및 알찬 구성에 만족함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>알찬 7+2 증정 구성 — 7입에 2입이 추가 증정되어 실속 있고 넉넉하게 섭취 가능함
-넉넉한 유통기한 — 개봉을 늦게 하더라도 유통기한이 넉넉하여 안심하고 복용함
-합리적인 가격대 — 좋은 구성의 제품을 착한 가격으로 구매할 수 있음</t>
+          <t>물 없는 간편한 섭취 — 상단 정제와 오렌지맛 액상을 물 없이 간편하게 복용함
+넉넉한 추가 증정 — 7입에 2입이 더해진 9입 구성으로 여분이 있어 반가움
+우수한 피로 회복 — 복용 후 피로가 풀어지고 에너지가 생김</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>액상·분말 혼합 캡슐 — 버튼을 누르면 액상과 분말이 섞이는 방식으로 누르고 마시기 편함
-목걸림 없는 가루 제형 — 알약 섭취 시 목에 걸리는 불편함 없이 편하게 복용할 수 있음
-맛있고 빠른 피로 회복 — 달달하고 상큼한 맛이며 섭취 후 피로 해소와 체력 충전 효과가 뛰어남</t>
+          <t>신선한 믹스형 용기 — 버튼을 눌러 액상과 분말을 직접 섞어 마시는 바이탈 캡 형태임
+목넘김 편한 가루 제형 — 가루 형태로 되어 있어 알약 이물감 없이 편하게 복용함
+우수한 피로 회복 효과 — 달콤상큼한 맛이며 피로 완화 및 혓바늘 개선에 도움을 줌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 바쁘거나 체력이 떨어질 때 복용 시 활력이 돋고 몸이 가벼워짐
-편리하고 빠른 배송 — 배송 상태가 양호하며 편리하게 챙겨 먹기 좋음</t>
+          <t>확실한 활력 개선 — 바쁜 일상이나 피로 상황에서 체력 및 활력 증진을 체감함
+안전한 배송 및 복용 — 포장 배송 상태가 양호하며 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 및 구성 — 유사 제품 대비 합리적인 가격과 알찬 성분 구성을 자랑함
-체감되는 건강 개선 — 복용 후 기대 이상으로 피로 회복 및 체력 관리 효과를 체감함
-간편한 일체형 휴대성 — 하루 한 병씩 챙겨 다니며 간편하게 복용할 수 있음</t>
+          <t>뛰어난 실속과 가성비 — 타 브랜드 대비 성분과 가격 면에서 실속 있음
+체감되는 피로 회복 — 복용 후 몸이 느낄 정도로 피로 회복 효과가 뛰어남
+부담 없는 맛 — 맛이 괜찮아 매일 거부감 없이 복용 가능함</t>
         </is>
       </c>
     </row>
@@ -3687,18 +3400,18 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 미동봉 아쉬움 — 선물용으로 적합하나 쇼핑백이 따로 동봉되지 않음</t>
+          <t>선물용 쇼핑백 누락 — 선물용 쇼핑백이 따로 동봉되지 않음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 제품 품질과 효능은 만족스러우나 가격대가 높게 느껴짐</t>
+          <t>부담스러운 가격 — 제품 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 박스 구김 — 배송 과정에서 제품 박스가 구겨져 도착하는 아쉬움이 있음</t>
+          <t>배송 중 상자 훼손 — 배송 과정에서 제품 박스가 구겨져서 도착함</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -3706,12 +3419,12 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 감기약 맛 — 오렌지 맛 감기약 느낌의 향과 맛이 나서 호불호가 존재함</t>
+          <t>약 맛 감기약 느낌 — 오렌지 맛 감기약 느낌이 나 맛에 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 미동봉 배송 — 선물용 구매 시 쇼핑백이 동봉되지 않아 아쉬움이 있음</t>
+          <t>쇼핑백 누락 — 쇼핑백이 동봉되지 않아 아쉬움</t>
         </is>
       </c>
     </row>
@@ -4008,12 +3721,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
     </row>
@@ -4065,12 +3778,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>"2개월분" 김종국 듀얼 아르기닌 &amp; 밀크씨슬 플러스 + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
     </row>
@@ -4142,10 +3855,10 @@
         <v>1956</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>1535</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>75</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4156,72 +3869,67 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지가 정성스럽고 고급스러워 선물용으로 만족도가 높음
-비리지 않고 맛있는 맛 — 비린 맛 없이 맛있게 마실 수 있어 꾸준한 복용이 용이함
-피부 탄력 관리 도움 — 하루 한 병 섭취로 피부가 촉촉해지고 탄력이 생기는 기분이 듦</t>
+          <t>고급스러운 선물 포장 — 오간자 및 플리츠백 구성으로 패키지가 고급스러움
+거부감 없는 맛 — 콜라겐 특유의 거부감 없이 맛있게 복용함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>풍성한 혜택 및 알찬 구성 — 효소와 단백질바, 포토카드까지 포함된 가성비 높고 알찬 구성임
-맛있는 가루 효소 — 크림소다, 베리말차 등 다양한 맛이 있어 거부감 없이 맛있음
-속 편한 소화 개선 — 위가 불편할 때 먹기 좋으며 영양을 간편하게 챙길 수 있음</t>
+          <t>알찬 기획 구성 — 효소와 단백질바, 포토카드까지 포함되어 기획 구성이 알참
+맛있는 효소 풍미 — 크림소다, 베리말차 등 여러 맛이 모두 맛있음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 속이 편안하고 빠른 회복이 가능함
-개별 포장의 우수한 휴대성 — 1포씩 깔끔하게 개별 포장되어 가방에 넣고 다니기 편리함
-넉넉한 15포 세트 구성 — 5포씩 3박스로 나뉘어 넉넉하게 보관하고 지인에게 나눌 수 있음</t>
+          <t>확실한 숙취 해소 — 음주 전후 상관없이 복용 시 다음 날 속이 편안함
+개별 포장 및 휴대성 — 개별 스틱 포장으로 가방에 하나씩 휴대하기 좋음
+알찬 3박스 세트 — 15포 세트 구성으로 넉넉하며 선물용으로 포장이 깔끔함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 더부룩함이 줄어들고 소화가 잘 되며 장 건강에 도움을 줌
-고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소한 맛이라 부담 없이 먹기 좋음
-풍성한 사은품 증정 — 추가 증정포와 견과류바 등 푸짐한 구성 혜택이 제공됨</t>
+          <t>속 편한 소화 촉진 — 더부룩한 속을 줄여주고 소화 및 배변 활동을 도움
+고소한 미숫가루 맛 — 텁텁함 없이 미숫가루처럼 구수하고 맛있음
+푸짐한 사은품 제공 — 견과류 박스 등 푸짐한 사은품이 동봉됨</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 다양한 종류와 맛으로 구성되어 식단 관리 시 질리지 않음
-촉촉하고 부드러운 식감 — 퍽퍽하지 않고 부드러워 부담 없이 맛있게 즐길 수 있음
-전자레인지용 용기 증정 — 증정된 용기로 전자레인지에 간편하게 데워 먹을 수 있음</t>
+          <t>다채로운 20종 구성 — 20가지 다채로운 구성으로 질리지 않고 섭취 가능함
+부드러운 닭가슴살 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 부드러움
+전용 용기 제공 — 전자레인지용 용기가 함께 제공되어 편리함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 달콤한 맛 — 비린 맛없이 달콤한 두유나 음료 느낌으로 맛있게 마실 수 있음
-포만감 및 간식 대용 — 마시면 배가 차서 간식이 당길 때나 포만감 유지에 도움 됨
-운동 후 단백질 보충 — 운동 후 간편하게 마시며 단백질을 챙기기에 적합함</t>
+          <t>비린 맛 없는 음료 감각 — 단백질 특유의 비린 맛이 없고 달달하여 음료처럼 마심
+포만감 및 단백질 충전 — 은근히 포만감이 있고 운동 후 단백질 보충에 유용함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>식후 빠른 소화 촉진 — 음식 섭취 후 복용 시 속이 편안해지고 소화가 잘 됨
-고소한 옥수수 맛 — 거부감 없는 옥수수 맛이며 물 없이도 간편하게 섭취 가능함
-맛있는 저당 견과류바 증정 — 사은품으로 함께 제공되는 저당 견과류바의 맛과 퀄리티가 우수함</t>
+          <t>우수한 소화 개선 — 식사 후 복용 시 소화를 한결 잘되게 해줌
+고소한 옥수수 맛 — 옥수수 맛이라 거부감이 없고 물 없이 복용 가능함
+맛있는 사은품 증정 — 사은품으로 증정되는 저당 견과류바의 맛과 만족도가 높음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 복용 시 피로가 줄고 운동 수행 능력 및 에너지가 개선됨
-고운 입자와 뛰어난 용해도 — 입자가 아주 고와서 물에 잘 녹아 섭취하기 편함
-대용량 및 뛰어난 가성비 — 100서빙의 넉넉한 용량 대비 가격이 저렴하여 가성비가 훌륭함</t>
+          <t>운동 수행 능력 향상 — 복용 시 피로가 줄고 운동 수행 능력 향상에 도움을 줌
+고운 입자와 우수한 용해 — 입자가 매우 고와 물에 잘 녹음
+높은 가성비 — 100서빙의 대용량 대비 가격이 저렴함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>아르기닌·밀크씨슬 올인원 — 활력과 간 건강을 동시에 챙길 수 있는 알찬 2개월분 구성임
-확실한 피로 회복 효과 — 복용 후 아침 일어남이 가벼워지고 일상 피로감이 줄어듦
-운동 및 일상 활력 증진 — 운동 집중도가 높아지고 컨디션 관리에 큰 도움이 됨</t>
+          <t>다양한 맛 구성 — 여러 종류의 맛으로 구성되어 질리지 않게 식단 관리함
+촉촉한 식감과 빠른 조리 — 닭가슴살이 촉촉하며 전자레인지로 간편하게 조리함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛 구성 — 종류가 다양하여 매일 질리지 않고 식단 관리를 할 수 있음
-촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 맛이 뛰어남
-간편한 전자레인지 조리 — 전자레인지에 쉽게 데워 먹을 수 있어 식사 대용으로 편리함</t>
+          <t>활력과 간 건강 케어 — 아르기닌과 밀크씨슬을 한 번에 섭취할 수 있어 효율적임
+피로 감소 효과 — 복용 후 피로가 감소하고 아침에 일어날 때 몸이 한결 가벼움</t>
         </is>
       </c>
     </row>
@@ -4233,12 +3941,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>오간자 포장 누락 — 오간자 포장이 누락된 상태로 배송되는 경우가 발생함</t>
+          <t>오간자 포장 누락 — 안내된 오간자 포장이 누락되어 배송됨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>증정 포토카드 구김 — 배송 포장 상태로 인해 증정 포토카드가 일부 구겨져 도착함</t>
+          <t>포토카드 구겨짐 — 증정 포토카드 일부가 구겨진 상태로 도착함</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
@@ -4247,12 +3955,12 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 끈 불량 배송 — 증정용 쇼핑백의 끈이 달려있지 않은 불량 상태로 배송됨</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 끈 누락 — 증정 쇼핑백에 끈이 달리지 않은 상태로 배송됨</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4302,12 +4010,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>64,200원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>64,200원</t>
         </is>
       </c>
     </row>
@@ -4948,663 +4656,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>1위</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2위</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>3위</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>4위</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>5위</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>6위</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>7위</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>8위</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>9위</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>10위</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="100" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>썸네일</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] 덴프스 트루바이타민 맥스 5종 택1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 120정 (4개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 14+1포 (15일분)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>평점</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>리뷰수</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>676</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>긍정리뷰</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>붓기 및 라인 관리 효과 — 야식이나 맵단짠 음식 섭취 후 붓기 제거와 라인 관리에 효과적임
-부담 없는 포도 맛 — 한약 맛 부담 없이 상큼한 포도주스 느낌으로 맛있게 먹을 수 있음
-물 없이 간편한 섭취 — 작은 액상 포 형태로 물 없이 짜 마실 수 있어 휴대와 섭취가 용이함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>부정리뷰</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>17,300원</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>13,500원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>26,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>18,800원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>35,000원</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A11"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>비율(%)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>카카오선물하기</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>